--- a/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_mn_2021_2025.xlsx
+++ b/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_mn_2021_2025.xlsx
@@ -626,7 +626,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>23-02-2021 08:30</t>
+          <t>2021-02-23 08:30:00</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
@@ -719,7 +719,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>22-02-2021 08:30</t>
+          <t>2021-02-22 08:30:00</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
@@ -812,7 +812,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T4" t="n">
@@ -907,7 +907,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>19-03-2021 08:30</t>
+          <t>2021-03-19 08:30:00</t>
         </is>
       </c>
       <c r="T5" t="n">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>20-04-2021 08:30</t>
+          <t>2021-04-20 08:30:00</t>
         </is>
       </c>
       <c r="T6" t="n">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>20-05-2021 08:30</t>
+          <t>2021-05-20 08:30:00</t>
         </is>
       </c>
       <c r="T7" t="n">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>21-06-2021 08:30</t>
+          <t>2021-06-21 08:30:00</t>
         </is>
       </c>
       <c r="T8" t="n">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>22-07-2021 08:30</t>
+          <t>2021-07-22 08:30:00</t>
         </is>
       </c>
       <c r="T9" t="n">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>20-08-2021 08:30</t>
+          <t>2021-08-20 08:30:00</t>
         </is>
       </c>
       <c r="T10" t="n">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>15-09-2021 08:30</t>
+          <t>2021-09-15 08:30:00</t>
         </is>
       </c>
       <c r="T11" t="n">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T12" t="n">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>20-11-2021 08:30</t>
+          <t>2021-11-20 08:30:00</t>
         </is>
       </c>
       <c r="T13" t="n">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>21-12-2021 08:30</t>
+          <t>2021-12-21 08:30:00</t>
         </is>
       </c>
       <c r="T14" t="n">
@@ -1857,7 +1857,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>25-02-2021 08:30</t>
+          <t>2021-02-25 08:30:00</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>29-04-2021 08:30</t>
+          <t>2021-04-29 08:30:00</t>
         </is>
       </c>
       <c r="T16" t="n">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>20-04-2021 08:30</t>
+          <t>2021-04-20 08:30:00</t>
         </is>
       </c>
       <c r="T17" t="n">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>27-04-2021 08:30</t>
+          <t>2021-04-27 08:30:00</t>
         </is>
       </c>
       <c r="T18" t="n">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>24-02-2021 08:30</t>
+          <t>2021-02-24 08:30:00</t>
         </is>
       </c>
       <c r="T19" t="n">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>26-05-2021 08:30</t>
+          <t>2021-05-26 08:30:00</t>
         </is>
       </c>
       <c r="T20" t="n">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>26-06-2021 08:30</t>
+          <t>2021-06-26 08:30:00</t>
         </is>
       </c>
       <c r="T21" t="n">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>28-07-2021 08:30</t>
+          <t>2021-07-28 08:30:00</t>
         </is>
       </c>
       <c r="T22" t="n">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>26-08-2021 08:30</t>
+          <t>2021-08-26 08:30:00</t>
         </is>
       </c>
       <c r="T23" t="n">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>22-09-2021 08:30</t>
+          <t>2021-09-22 08:30:00</t>
         </is>
       </c>
       <c r="T24" t="n">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T25" t="n">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>26-11-2021 08:30</t>
+          <t>2021-11-26 08:30:00</t>
         </is>
       </c>
       <c r="T26" t="n">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>28-12-2021 08:30</t>
+          <t>2021-12-28 08:30:00</t>
         </is>
       </c>
       <c r="T27" t="n">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T28" t="inlineStr"/>
@@ -3195,7 +3195,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>20-03-2021 08:30</t>
+          <t>2021-03-20 08:30:00</t>
         </is>
       </c>
       <c r="T29" t="inlineStr"/>
@@ -3288,7 +3288,7 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T30" t="inlineStr"/>
@@ -3381,7 +3381,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>20-03-2021 08:30</t>
+          <t>2021-03-20 08:30:00</t>
         </is>
       </c>
       <c r="T31" t="inlineStr"/>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T32" t="inlineStr"/>
@@ -3567,7 +3567,7 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>20-03-2021 08:30</t>
+          <t>2021-03-20 08:30:00</t>
         </is>
       </c>
       <c r="T33" t="inlineStr"/>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T34" t="inlineStr"/>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>20-03-2021 08:30</t>
+          <t>2021-03-20 08:30:00</t>
         </is>
       </c>
       <c r="T35" t="inlineStr"/>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T36" t="inlineStr"/>
@@ -3939,7 +3939,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>19-03-2021 08:30</t>
+          <t>2021-03-19 08:30:00</t>
         </is>
       </c>
       <c r="T37" t="inlineStr"/>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T38" t="inlineStr"/>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>20-03-2021 08:30</t>
+          <t>2021-03-20 08:30:00</t>
         </is>
       </c>
       <c r="T39" t="inlineStr"/>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T40" t="inlineStr"/>
@@ -4311,7 +4311,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>19-03-2021 08:30</t>
+          <t>2021-03-19 08:30:00</t>
         </is>
       </c>
       <c r="T41" t="inlineStr"/>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T42" t="inlineStr"/>
@@ -4497,7 +4497,7 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>20-03-2021 08:30</t>
+          <t>2021-03-20 08:30:00</t>
         </is>
       </c>
       <c r="T43" t="inlineStr"/>
@@ -4590,7 +4590,7 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T44" t="inlineStr"/>
@@ -4683,7 +4683,7 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>20-03-2021 08:30</t>
+          <t>2021-03-20 08:30:00</t>
         </is>
       </c>
       <c r="T45" t="inlineStr"/>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>24-02-2021 08:30</t>
+          <t>2021-02-24 08:30:00</t>
         </is>
       </c>
       <c r="T46" t="inlineStr"/>
@@ -4869,7 +4869,7 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>27-04-2021 08:30</t>
+          <t>2021-04-27 08:30:00</t>
         </is>
       </c>
       <c r="T47" t="n">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T48" t="inlineStr"/>
@@ -5061,7 +5061,7 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T49" t="inlineStr"/>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T50" t="inlineStr"/>
@@ -5247,7 +5247,7 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T51" t="inlineStr"/>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>19-03-2021 08:30</t>
+          <t>2021-03-19 08:30:00</t>
         </is>
       </c>
       <c r="T52" t="inlineStr"/>
@@ -5433,7 +5433,7 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>25-02-2021 08:30</t>
+          <t>2021-02-25 08:30:00</t>
         </is>
       </c>
       <c r="T53" t="inlineStr"/>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>25-02-2021 08:30</t>
+          <t>2021-02-25 08:30:00</t>
         </is>
       </c>
       <c r="T54" t="inlineStr"/>
@@ -5619,7 +5619,7 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>27-02-2021 08:30</t>
+          <t>2021-02-27 08:30:00</t>
         </is>
       </c>
       <c r="T55" t="inlineStr"/>
@@ -5712,7 +5712,7 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>24-02-2021 08:30</t>
+          <t>2021-02-24 08:30:00</t>
         </is>
       </c>
       <c r="T56" t="n">
@@ -5807,7 +5807,7 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>26-05-2021 08:30</t>
+          <t>2021-05-26 08:30:00</t>
         </is>
       </c>
       <c r="T57" t="n">
@@ -5902,7 +5902,7 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>26-06-2021 08:30</t>
+          <t>2021-06-26 08:30:00</t>
         </is>
       </c>
       <c r="T58" t="n">
@@ -5997,7 +5997,7 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>28-07-2021 08:30</t>
+          <t>2021-07-28 08:30:00</t>
         </is>
       </c>
       <c r="T59" t="n">
@@ -6092,7 +6092,7 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>26-08-2021 08:30</t>
+          <t>2021-08-26 08:30:00</t>
         </is>
       </c>
       <c r="T60" t="n">
@@ -6187,7 +6187,7 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>22-09-2021 08:30</t>
+          <t>2021-09-22 08:30:00</t>
         </is>
       </c>
       <c r="T61" t="n">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T62" t="n">
@@ -6377,7 +6377,7 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>26-11-2021 08:30</t>
+          <t>2021-11-26 08:30:00</t>
         </is>
       </c>
       <c r="T63" t="n">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>28-12-2021 08:30</t>
+          <t>2021-12-28 08:30:00</t>
         </is>
       </c>
       <c r="T64" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>29-04-2021 08:30</t>
+          <t>2021-04-29 08:30:00</t>
         </is>
       </c>
       <c r="T65" t="n">
@@ -6666,7 +6666,7 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>24-02-2021 08:30</t>
+          <t>2021-02-24 08:30:00</t>
         </is>
       </c>
       <c r="T66" t="n">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>26-05-2021 08:30</t>
+          <t>2021-05-26 08:30:00</t>
         </is>
       </c>
       <c r="T67" t="n">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>26-06-2021 08:30</t>
+          <t>2021-06-26 08:30:00</t>
         </is>
       </c>
       <c r="T68" t="n">
@@ -6951,7 +6951,7 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>28-07-2021 08:30</t>
+          <t>2021-07-28 08:30:00</t>
         </is>
       </c>
       <c r="T69" t="n">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>26-08-2021 08:30</t>
+          <t>2021-08-26 08:30:00</t>
         </is>
       </c>
       <c r="T70" t="n">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>22-09-2021 08:30</t>
+          <t>2021-09-22 08:30:00</t>
         </is>
       </c>
       <c r="T71" t="n">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T72" t="n">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>28-12-2021 08:30</t>
+          <t>2021-12-28 08:30:00</t>
         </is>
       </c>
       <c r="T73" t="n">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T74" t="n">
@@ -7521,7 +7521,7 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>19-03-2021 08:30</t>
+          <t>2021-03-19 08:30:00</t>
         </is>
       </c>
       <c r="T75" t="n">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>20-05-2021 08:30</t>
+          <t>2021-05-20 08:30:00</t>
         </is>
       </c>
       <c r="T76" t="n">
@@ -7711,7 +7711,7 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>22-07-2021 08:30</t>
+          <t>2021-07-22 08:30:00</t>
         </is>
       </c>
       <c r="T77" t="n">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>20-08-2021 08:30</t>
+          <t>2021-08-20 08:30:00</t>
         </is>
       </c>
       <c r="T78" t="n">
@@ -7901,7 +7901,7 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>15-09-2021 08:30</t>
+          <t>2021-09-15 08:30:00</t>
         </is>
       </c>
       <c r="T79" t="n">
@@ -7996,7 +7996,7 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T80" t="n">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>20-11-2021 08:30</t>
+          <t>2021-11-20 08:30:00</t>
         </is>
       </c>
       <c r="T81" t="n">
@@ -8186,7 +8186,7 @@
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>21-12-2021 08:30</t>
+          <t>2021-12-21 08:30:00</t>
         </is>
       </c>
       <c r="T82" t="n">
@@ -8281,7 +8281,7 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>25-02-2021 08:30</t>
+          <t>2021-02-25 08:30:00</t>
         </is>
       </c>
       <c r="T83" t="inlineStr"/>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>27-05-2021 08:30</t>
+          <t>2021-05-27 08:30:00</t>
         </is>
       </c>
       <c r="T84" t="n">
@@ -8469,7 +8469,7 @@
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>28-06-2021 08:30</t>
+          <t>2021-06-28 08:30:00</t>
         </is>
       </c>
       <c r="T85" t="n">
@@ -8564,7 +8564,7 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>29-07-2021 08:30</t>
+          <t>2021-07-29 08:30:00</t>
         </is>
       </c>
       <c r="T86" t="n">
@@ -8659,7 +8659,7 @@
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>27-08-2021 08:30</t>
+          <t>2021-08-27 08:30:00</t>
         </is>
       </c>
       <c r="T87" t="n">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>24-09-2021 08:30</t>
+          <t>2021-09-24 08:30:00</t>
         </is>
       </c>
       <c r="T88" t="n">
@@ -8849,7 +8849,7 @@
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>28-10-2021 08:30</t>
+          <t>2021-10-28 08:30:00</t>
         </is>
       </c>
       <c r="T89" t="n">
@@ -8944,7 +8944,7 @@
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>27-11-2021 08:30</t>
+          <t>2021-11-27 08:30:00</t>
         </is>
       </c>
       <c r="T90" t="n">
@@ -9039,7 +9039,7 @@
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>29-12-2021 08:30</t>
+          <t>2021-12-29 08:30:00</t>
         </is>
       </c>
       <c r="T91" t="n">
@@ -9134,7 +9134,7 @@
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>25-02-2021 08:30</t>
+          <t>2021-02-25 08:30:00</t>
         </is>
       </c>
       <c r="T92" t="n">
@@ -9229,7 +9229,7 @@
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>27-05-2021 08:30</t>
+          <t>2021-05-27 08:30:00</t>
         </is>
       </c>
       <c r="T93" t="n">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>28-06-2021 08:30</t>
+          <t>2021-06-28 08:30:00</t>
         </is>
       </c>
       <c r="T94" t="n">
@@ -9419,7 +9419,7 @@
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>29-07-2021 08:30</t>
+          <t>2021-07-29 08:30:00</t>
         </is>
       </c>
       <c r="T95" t="n">
@@ -9514,7 +9514,7 @@
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>27-08-2021 08:30</t>
+          <t>2021-08-27 08:30:00</t>
         </is>
       </c>
       <c r="T96" t="n">
@@ -9609,7 +9609,7 @@
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>24-09-2021 08:30</t>
+          <t>2021-09-24 08:30:00</t>
         </is>
       </c>
       <c r="T97" t="n">
@@ -9704,7 +9704,7 @@
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>28-10-2021 08:30</t>
+          <t>2021-10-28 08:30:00</t>
         </is>
       </c>
       <c r="T98" t="n">
@@ -9799,7 +9799,7 @@
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>27-11-2021 08:30</t>
+          <t>2021-11-27 08:30:00</t>
         </is>
       </c>
       <c r="T99" t="n">
@@ -9894,7 +9894,7 @@
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>29-12-2021 08:30</t>
+          <t>2021-12-29 08:30:00</t>
         </is>
       </c>
       <c r="T100" t="n">
@@ -9989,7 +9989,7 @@
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>25-02-2021 08:30</t>
+          <t>2021-02-25 08:30:00</t>
         </is>
       </c>
       <c r="T101" t="n">
@@ -10084,7 +10084,7 @@
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>27-05-2021 08:30</t>
+          <t>2021-05-27 08:30:00</t>
         </is>
       </c>
       <c r="T102" t="n">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>28-06-2021 08:30</t>
+          <t>2021-06-28 08:30:00</t>
         </is>
       </c>
       <c r="T103" t="n">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>29-07-2021 08:30</t>
+          <t>2021-07-29 08:30:00</t>
         </is>
       </c>
       <c r="T104" t="n">
@@ -10369,7 +10369,7 @@
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>27-08-2021 08:30</t>
+          <t>2021-08-27 08:30:00</t>
         </is>
       </c>
       <c r="T105" t="n">
@@ -10464,7 +10464,7 @@
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>24-09-2021 08:30</t>
+          <t>2021-09-24 08:30:00</t>
         </is>
       </c>
       <c r="T106" t="n">
@@ -10559,7 +10559,7 @@
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T107" t="n">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>27-11-2021 08:30</t>
+          <t>2021-11-27 08:30:00</t>
         </is>
       </c>
       <c r="T108" t="n">
@@ -10749,7 +10749,7 @@
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>29-12-2021 08:30</t>
+          <t>2021-12-29 08:30:00</t>
         </is>
       </c>
       <c r="T109" t="n">
@@ -10844,7 +10844,7 @@
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>25-02-2021 08:30</t>
+          <t>2021-02-25 08:30:00</t>
         </is>
       </c>
       <c r="T110" t="n">
@@ -10939,7 +10939,7 @@
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>27-05-2021 08:30</t>
+          <t>2021-05-27 08:30:00</t>
         </is>
       </c>
       <c r="T111" t="n">
@@ -11034,7 +11034,7 @@
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>26-06-2021 08:30</t>
+          <t>2021-06-26 08:30:00</t>
         </is>
       </c>
       <c r="T112" t="n">
@@ -11129,7 +11129,7 @@
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>29-07-2021 08:30</t>
+          <t>2021-07-29 08:30:00</t>
         </is>
       </c>
       <c r="T113" t="n">
@@ -11224,7 +11224,7 @@
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>27-08-2021 08:30</t>
+          <t>2021-08-27 08:30:00</t>
         </is>
       </c>
       <c r="T114" t="n">
@@ -11319,7 +11319,7 @@
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>22-09-2021 08:30</t>
+          <t>2021-09-22 08:30:00</t>
         </is>
       </c>
       <c r="T115" t="n">
@@ -11414,7 +11414,7 @@
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>28-10-2021 08:30</t>
+          <t>2021-10-28 08:30:00</t>
         </is>
       </c>
       <c r="T116" t="n">
@@ -11509,7 +11509,7 @@
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>27-11-2021 08:30</t>
+          <t>2021-11-27 08:30:00</t>
         </is>
       </c>
       <c r="T117" t="n">
@@ -11604,7 +11604,7 @@
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>29-12-2021 08:30</t>
+          <t>2021-12-29 08:30:00</t>
         </is>
       </c>
       <c r="T118" t="n">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>24-02-2021 08:30</t>
+          <t>2021-02-24 08:30:00</t>
         </is>
       </c>
       <c r="T119" t="inlineStr"/>
@@ -11792,7 +11792,7 @@
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>24-02-2021 08:30</t>
+          <t>2021-02-24 08:30:00</t>
         </is>
       </c>
       <c r="T120" t="inlineStr"/>
@@ -11885,7 +11885,7 @@
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>26-05-2021 08:30</t>
+          <t>2021-05-26 08:30:00</t>
         </is>
       </c>
       <c r="T121" t="n">
@@ -11980,7 +11980,7 @@
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>26-06-2021 08:30</t>
+          <t>2021-06-26 08:30:00</t>
         </is>
       </c>
       <c r="T122" t="n">
@@ -12075,7 +12075,7 @@
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>26-08-2021 08:30</t>
+          <t>2021-08-26 08:30:00</t>
         </is>
       </c>
       <c r="T123" t="n">
@@ -12170,7 +12170,7 @@
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>22-09-2021 08:30</t>
+          <t>2021-09-22 08:30:00</t>
         </is>
       </c>
       <c r="T124" t="n">
@@ -12265,7 +12265,7 @@
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T125" t="n">
@@ -12360,7 +12360,7 @@
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>26-11-2021 08:30</t>
+          <t>2021-11-26 08:30:00</t>
         </is>
       </c>
       <c r="T126" t="n">
@@ -12455,7 +12455,7 @@
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>28-12-2021 08:30</t>
+          <t>2021-12-28 08:30:00</t>
         </is>
       </c>
       <c r="T127" t="n">
@@ -12550,7 +12550,7 @@
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>30-04-2021 08:30</t>
+          <t>2021-04-30 08:30:00</t>
         </is>
       </c>
       <c r="T128" t="n">
@@ -12649,7 +12649,7 @@
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T129" t="inlineStr"/>
@@ -12742,7 +12742,7 @@
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T130" t="inlineStr"/>
@@ -12835,7 +12835,7 @@
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>19-03-2021 08:30</t>
+          <t>2021-03-19 08:30:00</t>
         </is>
       </c>
       <c r="T131" t="inlineStr"/>
@@ -12928,7 +12928,7 @@
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T132" t="inlineStr"/>
@@ -13021,7 +13021,7 @@
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>19-03-2021 08:30</t>
+          <t>2021-03-19 08:30:00</t>
         </is>
       </c>
       <c r="T133" t="inlineStr"/>
@@ -13114,7 +13114,7 @@
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T134" t="n">
@@ -13209,7 +13209,7 @@
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t>20-03-2021 08:30</t>
+          <t>2021-03-20 08:30:00</t>
         </is>
       </c>
       <c r="T135" t="n">
@@ -13304,7 +13304,7 @@
       </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t>21-05-2021 08:30</t>
+          <t>2021-05-21 08:30:00</t>
         </is>
       </c>
       <c r="T136" t="n">
@@ -13399,7 +13399,7 @@
       </c>
       <c r="S137" t="inlineStr">
         <is>
-          <t>22-06-2021 08:30</t>
+          <t>2021-06-22 08:30:00</t>
         </is>
       </c>
       <c r="T137" t="n">
@@ -13494,7 +13494,7 @@
       </c>
       <c r="S138" t="inlineStr">
         <is>
-          <t>23-07-2021 08:30</t>
+          <t>2021-07-23 08:30:00</t>
         </is>
       </c>
       <c r="T138" t="n">
@@ -13589,7 +13589,7 @@
       </c>
       <c r="S139" t="inlineStr">
         <is>
-          <t>21-08-2021 08:30</t>
+          <t>2021-08-21 08:30:00</t>
         </is>
       </c>
       <c r="T139" t="n">
@@ -13684,7 +13684,7 @@
       </c>
       <c r="S140" t="inlineStr">
         <is>
-          <t>16-09-2021 08:30</t>
+          <t>2021-09-16 08:30:00</t>
         </is>
       </c>
       <c r="T140" t="n">
@@ -13779,7 +13779,7 @@
       </c>
       <c r="S141" t="inlineStr">
         <is>
-          <t>22-10-2021 08:30</t>
+          <t>2021-10-22 08:30:00</t>
         </is>
       </c>
       <c r="T141" t="n">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="S142" t="inlineStr">
         <is>
-          <t>22-11-2021 08:30</t>
+          <t>2021-11-22 08:30:00</t>
         </is>
       </c>
       <c r="T142" t="n">
@@ -13969,7 +13969,7 @@
       </c>
       <c r="S143" t="inlineStr">
         <is>
-          <t>22-12-2021 08:30</t>
+          <t>2021-12-22 08:30:00</t>
         </is>
       </c>
       <c r="T143" t="n">
@@ -14064,7 +14064,7 @@
       </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t>24-04-2021 08:30</t>
+          <t>2021-04-24 08:30:00</t>
         </is>
       </c>
       <c r="T144" t="n">
@@ -14163,7 +14163,7 @@
       </c>
       <c r="S145" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T145" t="n">
@@ -14258,7 +14258,7 @@
       </c>
       <c r="S146" t="inlineStr">
         <is>
-          <t>19-03-2021 08:30</t>
+          <t>2021-03-19 08:30:00</t>
         </is>
       </c>
       <c r="T146" t="n">
@@ -14353,7 +14353,7 @@
       </c>
       <c r="S147" t="inlineStr">
         <is>
-          <t>20-05-2021 08:30</t>
+          <t>2021-05-20 08:30:00</t>
         </is>
       </c>
       <c r="T147" t="n">
@@ -14448,7 +14448,7 @@
       </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t>21-06-2021 08:30</t>
+          <t>2021-06-21 08:30:00</t>
         </is>
       </c>
       <c r="T148" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="S149" t="inlineStr">
         <is>
-          <t>22-07-2021 08:30</t>
+          <t>2021-07-22 08:30:00</t>
         </is>
       </c>
       <c r="T149" t="n">
@@ -14638,7 +14638,7 @@
       </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t>20-08-2021 08:30</t>
+          <t>2021-08-20 08:30:00</t>
         </is>
       </c>
       <c r="T150" t="n">
@@ -14733,7 +14733,7 @@
       </c>
       <c r="S151" t="inlineStr">
         <is>
-          <t>15-09-2021 08:30</t>
+          <t>2021-09-15 08:30:00</t>
         </is>
       </c>
       <c r="T151" t="n">
@@ -14828,7 +14828,7 @@
       </c>
       <c r="S152" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T152" t="n">
@@ -14923,7 +14923,7 @@
       </c>
       <c r="S153" t="inlineStr">
         <is>
-          <t>20-11-2021 08:30</t>
+          <t>2021-11-20 08:30:00</t>
         </is>
       </c>
       <c r="T153" t="n">
@@ -15018,7 +15018,7 @@
       </c>
       <c r="S154" t="inlineStr">
         <is>
-          <t>21-12-2021 08:30</t>
+          <t>2021-12-21 08:30:00</t>
         </is>
       </c>
       <c r="T154" t="n">
@@ -15113,7 +15113,7 @@
       </c>
       <c r="S155" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T155" t="n">
@@ -15208,7 +15208,7 @@
       </c>
       <c r="S156" t="inlineStr">
         <is>
-          <t>21-05-2021 08:30</t>
+          <t>2021-05-21 08:30:00</t>
         </is>
       </c>
       <c r="T156" t="n">
@@ -15303,7 +15303,7 @@
       </c>
       <c r="S157" t="inlineStr">
         <is>
-          <t>22-06-2021 08:30</t>
+          <t>2021-06-22 08:30:00</t>
         </is>
       </c>
       <c r="T157" t="n">
@@ -15398,7 +15398,7 @@
       </c>
       <c r="S158" t="inlineStr">
         <is>
-          <t>23-07-2021 08:30</t>
+          <t>2021-07-23 08:30:00</t>
         </is>
       </c>
       <c r="T158" t="n">
@@ -15493,7 +15493,7 @@
       </c>
       <c r="S159" t="inlineStr">
         <is>
-          <t>21-08-2021 08:30</t>
+          <t>2021-08-21 08:30:00</t>
         </is>
       </c>
       <c r="T159" t="n">
@@ -15588,7 +15588,7 @@
       </c>
       <c r="S160" t="inlineStr">
         <is>
-          <t>16-09-2021 08:30</t>
+          <t>2021-09-16 08:30:00</t>
         </is>
       </c>
       <c r="T160" t="n">
@@ -15683,7 +15683,7 @@
       </c>
       <c r="S161" t="inlineStr">
         <is>
-          <t>22-10-2021 08:30</t>
+          <t>2021-10-22 08:30:00</t>
         </is>
       </c>
       <c r="T161" t="n">
@@ -15778,7 +15778,7 @@
       </c>
       <c r="S162" t="inlineStr">
         <is>
-          <t>22-11-2021 08:30</t>
+          <t>2021-11-22 08:30:00</t>
         </is>
       </c>
       <c r="T162" t="n">
@@ -15873,7 +15873,7 @@
       </c>
       <c r="S163" t="inlineStr">
         <is>
-          <t>22-12-2021 08:30</t>
+          <t>2021-12-22 08:30:00</t>
         </is>
       </c>
       <c r="T163" t="n">
@@ -15968,7 +15968,7 @@
       </c>
       <c r="S164" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T164" t="n">
@@ -16063,7 +16063,7 @@
       </c>
       <c r="S165" t="inlineStr">
         <is>
-          <t>19-03-2021 08:30</t>
+          <t>2021-03-19 08:30:00</t>
         </is>
       </c>
       <c r="T165" t="n">
@@ -16158,7 +16158,7 @@
       </c>
       <c r="S166" t="inlineStr">
         <is>
-          <t>20-05-2021 08:30</t>
+          <t>2021-05-20 08:30:00</t>
         </is>
       </c>
       <c r="T166" t="n">
@@ -16253,7 +16253,7 @@
       </c>
       <c r="S167" t="inlineStr">
         <is>
-          <t>21-06-2021 08:30</t>
+          <t>2021-06-21 08:30:00</t>
         </is>
       </c>
       <c r="T167" t="n">
@@ -16348,7 +16348,7 @@
       </c>
       <c r="S168" t="inlineStr">
         <is>
-          <t>22-07-2021 08:30</t>
+          <t>2021-07-22 08:30:00</t>
         </is>
       </c>
       <c r="T168" t="n">
@@ -16443,7 +16443,7 @@
       </c>
       <c r="S169" t="inlineStr">
         <is>
-          <t>20-08-2021 08:30</t>
+          <t>2021-08-20 08:30:00</t>
         </is>
       </c>
       <c r="T169" t="n">
@@ -16538,7 +16538,7 @@
       </c>
       <c r="S170" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T170" t="n">
@@ -16633,7 +16633,7 @@
       </c>
       <c r="S171" t="inlineStr">
         <is>
-          <t>20-11-2021 08:30</t>
+          <t>2021-11-20 08:30:00</t>
         </is>
       </c>
       <c r="T171" t="n">
@@ -16728,7 +16728,7 @@
       </c>
       <c r="S172" t="inlineStr">
         <is>
-          <t>21-12-2021 08:30</t>
+          <t>2021-12-21 08:30:00</t>
         </is>
       </c>
       <c r="T172" t="n">
@@ -16823,7 +16823,7 @@
       </c>
       <c r="S173" t="inlineStr">
         <is>
-          <t>25-02-2021 08:30</t>
+          <t>2021-02-25 08:30:00</t>
         </is>
       </c>
       <c r="T173" t="n">
@@ -16918,7 +16918,7 @@
       </c>
       <c r="S174" t="inlineStr">
         <is>
-          <t>27-05-2021 08:30</t>
+          <t>2021-05-27 08:30:00</t>
         </is>
       </c>
       <c r="T174" t="n">
@@ -17013,7 +17013,7 @@
       </c>
       <c r="S175" t="inlineStr">
         <is>
-          <t>28-06-2021 08:30</t>
+          <t>2021-06-28 08:30:00</t>
         </is>
       </c>
       <c r="T175" t="n">
@@ -17108,7 +17108,7 @@
       </c>
       <c r="S176" t="inlineStr">
         <is>
-          <t>27-08-2021 08:30</t>
+          <t>2021-08-27 08:30:00</t>
         </is>
       </c>
       <c r="T176" t="n">
@@ -17203,7 +17203,7 @@
       </c>
       <c r="S177" t="inlineStr">
         <is>
-          <t>24-09-2021 08:30</t>
+          <t>2021-09-24 08:30:00</t>
         </is>
       </c>
       <c r="T177" t="n">
@@ -17298,7 +17298,7 @@
       </c>
       <c r="S178" t="inlineStr">
         <is>
-          <t>28-10-2021 08:30</t>
+          <t>2021-10-28 08:30:00</t>
         </is>
       </c>
       <c r="T178" t="n">
@@ -17393,7 +17393,7 @@
       </c>
       <c r="S179" t="inlineStr">
         <is>
-          <t>29-12-2021 08:30</t>
+          <t>2021-12-29 08:30:00</t>
         </is>
       </c>
       <c r="T179" t="n">
@@ -17488,7 +17488,7 @@
       </c>
       <c r="S180" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T180" t="n">
@@ -17583,7 +17583,7 @@
       </c>
       <c r="S181" t="inlineStr">
         <is>
-          <t>19-03-2021 08:30</t>
+          <t>2021-03-19 08:30:00</t>
         </is>
       </c>
       <c r="T181" t="n">
@@ -17678,7 +17678,7 @@
       </c>
       <c r="S182" t="inlineStr">
         <is>
-          <t>20-05-2021 08:30</t>
+          <t>2021-05-20 08:30:00</t>
         </is>
       </c>
       <c r="T182" t="n">
@@ -17773,7 +17773,7 @@
       </c>
       <c r="S183" t="inlineStr">
         <is>
-          <t>21-06-2021 08:30</t>
+          <t>2021-06-21 08:30:00</t>
         </is>
       </c>
       <c r="T183" t="n">
@@ -17868,7 +17868,7 @@
       </c>
       <c r="S184" t="inlineStr">
         <is>
-          <t>22-07-2021 08:30</t>
+          <t>2021-07-22 08:30:00</t>
         </is>
       </c>
       <c r="T184" t="n">
@@ -17963,7 +17963,7 @@
       </c>
       <c r="S185" t="inlineStr">
         <is>
-          <t>20-08-2021 08:30</t>
+          <t>2021-08-20 08:30:00</t>
         </is>
       </c>
       <c r="T185" t="n">
@@ -18058,7 +18058,7 @@
       </c>
       <c r="S186" t="inlineStr">
         <is>
-          <t>15-09-2021 08:30</t>
+          <t>2021-09-15 08:30:00</t>
         </is>
       </c>
       <c r="T186" t="n">
@@ -18153,7 +18153,7 @@
       </c>
       <c r="S187" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T187" t="n">
@@ -18248,7 +18248,7 @@
       </c>
       <c r="S188" t="inlineStr">
         <is>
-          <t>20-11-2021 08:30</t>
+          <t>2021-11-20 08:30:00</t>
         </is>
       </c>
       <c r="T188" t="n">
@@ -18343,7 +18343,7 @@
       </c>
       <c r="S189" t="inlineStr">
         <is>
-          <t>21-12-2021 08:30</t>
+          <t>2021-12-21 08:30:00</t>
         </is>
       </c>
       <c r="T189" t="n">
@@ -18438,7 +18438,7 @@
       </c>
       <c r="S190" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T190" t="n">
@@ -18533,7 +18533,7 @@
       </c>
       <c r="S191" t="inlineStr">
         <is>
-          <t>19-03-2021 08:30</t>
+          <t>2021-03-19 08:30:00</t>
         </is>
       </c>
       <c r="T191" t="n">
@@ -18628,7 +18628,7 @@
       </c>
       <c r="S192" t="inlineStr">
         <is>
-          <t>20-05-2021 08:30</t>
+          <t>2021-05-20 08:30:00</t>
         </is>
       </c>
       <c r="T192" t="n">
@@ -18723,7 +18723,7 @@
       </c>
       <c r="S193" t="inlineStr">
         <is>
-          <t>21-06-2021 08:30</t>
+          <t>2021-06-21 08:30:00</t>
         </is>
       </c>
       <c r="T193" t="n">
@@ -18818,7 +18818,7 @@
       </c>
       <c r="S194" t="inlineStr">
         <is>
-          <t>22-07-2021 08:30</t>
+          <t>2021-07-22 08:30:00</t>
         </is>
       </c>
       <c r="T194" t="n">
@@ -18913,7 +18913,7 @@
       </c>
       <c r="S195" t="inlineStr">
         <is>
-          <t>20-08-2021 08:30</t>
+          <t>2021-08-20 08:30:00</t>
         </is>
       </c>
       <c r="T195" t="n">
@@ -19008,7 +19008,7 @@
       </c>
       <c r="S196" t="inlineStr">
         <is>
-          <t>15-09-2021 08:30</t>
+          <t>2021-09-15 08:30:00</t>
         </is>
       </c>
       <c r="T196" t="n">
@@ -19103,7 +19103,7 @@
       </c>
       <c r="S197" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T197" t="n">
@@ -19198,7 +19198,7 @@
       </c>
       <c r="S198" t="inlineStr">
         <is>
-          <t>20-11-2021 08:30</t>
+          <t>2021-11-20 08:30:00</t>
         </is>
       </c>
       <c r="T198" t="n">
@@ -19293,7 +19293,7 @@
       </c>
       <c r="S199" t="inlineStr">
         <is>
-          <t>21-12-2021 08:30</t>
+          <t>2021-12-21 08:30:00</t>
         </is>
       </c>
       <c r="T199" t="n">
@@ -19388,7 +19388,7 @@
       </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t>24-02-2021 08:30</t>
+          <t>2021-02-24 08:30:00</t>
         </is>
       </c>
       <c r="T200" t="n">
@@ -19483,7 +19483,7 @@
       </c>
       <c r="S201" t="inlineStr">
         <is>
-          <t>26-05-2021 08:30</t>
+          <t>2021-05-26 08:30:00</t>
         </is>
       </c>
       <c r="T201" t="n">
@@ -19578,7 +19578,7 @@
       </c>
       <c r="S202" t="inlineStr">
         <is>
-          <t>26-06-2021 08:30</t>
+          <t>2021-06-26 08:30:00</t>
         </is>
       </c>
       <c r="T202" t="n">
@@ -19673,7 +19673,7 @@
       </c>
       <c r="S203" t="inlineStr">
         <is>
-          <t>28-07-2021 08:30</t>
+          <t>2021-07-28 08:30:00</t>
         </is>
       </c>
       <c r="T203" t="n">
@@ -19768,7 +19768,7 @@
       </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t>26-08-2021 08:30</t>
+          <t>2021-08-26 08:30:00</t>
         </is>
       </c>
       <c r="T204" t="n">
@@ -19863,7 +19863,7 @@
       </c>
       <c r="S205" t="inlineStr">
         <is>
-          <t>22-09-2021 08:30</t>
+          <t>2021-09-22 08:30:00</t>
         </is>
       </c>
       <c r="T205" t="n">
@@ -19958,7 +19958,7 @@
       </c>
       <c r="S206" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T206" t="n">
@@ -20053,7 +20053,7 @@
       </c>
       <c r="S207" t="inlineStr">
         <is>
-          <t>26-11-2021 08:30</t>
+          <t>2021-11-26 08:30:00</t>
         </is>
       </c>
       <c r="T207" t="n">
@@ -20148,7 +20148,7 @@
       </c>
       <c r="S208" t="inlineStr">
         <is>
-          <t>28-12-2021 08:30</t>
+          <t>2021-12-28 08:30:00</t>
         </is>
       </c>
       <c r="T208" t="n">
@@ -20243,7 +20243,7 @@
       </c>
       <c r="S209" t="inlineStr">
         <is>
-          <t>24-02-2021 08:30</t>
+          <t>2021-02-24 08:30:00</t>
         </is>
       </c>
       <c r="T209" t="n">
@@ -20338,7 +20338,7 @@
       </c>
       <c r="S210" t="inlineStr">
         <is>
-          <t>26-05-2021 08:30</t>
+          <t>2021-05-26 08:30:00</t>
         </is>
       </c>
       <c r="T210" t="n">
@@ -20433,7 +20433,7 @@
       </c>
       <c r="S211" t="inlineStr">
         <is>
-          <t>26-06-2021 08:30</t>
+          <t>2021-06-26 08:30:00</t>
         </is>
       </c>
       <c r="T211" t="n">
@@ -20528,7 +20528,7 @@
       </c>
       <c r="S212" t="inlineStr">
         <is>
-          <t>28-07-2021 08:30</t>
+          <t>2021-07-28 08:30:00</t>
         </is>
       </c>
       <c r="T212" t="n">
@@ -20623,7 +20623,7 @@
       </c>
       <c r="S213" t="inlineStr">
         <is>
-          <t>26-08-2021 08:30</t>
+          <t>2021-08-26 08:30:00</t>
         </is>
       </c>
       <c r="T213" t="n">
@@ -20718,7 +20718,7 @@
       </c>
       <c r="S214" t="inlineStr">
         <is>
-          <t>22-09-2021 08:30</t>
+          <t>2021-09-22 08:30:00</t>
         </is>
       </c>
       <c r="T214" t="n">
@@ -20813,7 +20813,7 @@
       </c>
       <c r="S215" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T215" t="n">
@@ -20908,7 +20908,7 @@
       </c>
       <c r="S216" t="inlineStr">
         <is>
-          <t>26-11-2021 08:30</t>
+          <t>2021-11-26 08:30:00</t>
         </is>
       </c>
       <c r="T216" t="n">
@@ -21003,7 +21003,7 @@
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>28-12-2021 08:30</t>
+          <t>2021-12-28 08:30:00</t>
         </is>
       </c>
       <c r="T217" t="n">
@@ -21098,7 +21098,7 @@
       </c>
       <c r="S218" t="inlineStr">
         <is>
-          <t>24-02-2021 08:30</t>
+          <t>2021-02-24 08:30:00</t>
         </is>
       </c>
       <c r="T218" t="inlineStr"/>
@@ -21191,7 +21191,7 @@
       </c>
       <c r="S219" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T219" t="inlineStr"/>
@@ -21284,7 +21284,7 @@
       </c>
       <c r="S220" t="inlineStr">
         <is>
-          <t>19-03-2021 08:30</t>
+          <t>2021-03-19 08:30:00</t>
         </is>
       </c>
       <c r="T220" t="inlineStr"/>
@@ -21377,7 +21377,7 @@
       </c>
       <c r="S221" t="inlineStr">
         <is>
-          <t>20-02-2021 08:30</t>
+          <t>2021-02-20 08:30:00</t>
         </is>
       </c>
       <c r="T221" t="inlineStr"/>
@@ -21470,7 +21470,7 @@
       </c>
       <c r="S222" t="inlineStr">
         <is>
-          <t>20-02-2021 08:30</t>
+          <t>2021-02-20 08:30:00</t>
         </is>
       </c>
       <c r="T222" t="inlineStr"/>
@@ -21563,7 +21563,7 @@
       </c>
       <c r="S223" t="inlineStr">
         <is>
-          <t>24-02-2021 08:30</t>
+          <t>2021-02-24 08:30:00</t>
         </is>
       </c>
       <c r="T223" t="inlineStr"/>
@@ -21656,7 +21656,7 @@
       </c>
       <c r="S224" t="inlineStr">
         <is>
-          <t>24-02-2021 08:30</t>
+          <t>2021-02-24 08:30:00</t>
         </is>
       </c>
       <c r="T224" t="inlineStr"/>
@@ -21749,7 +21749,7 @@
       </c>
       <c r="S225" t="inlineStr">
         <is>
-          <t>24-02-2021 08:30</t>
+          <t>2021-02-24 08:30:00</t>
         </is>
       </c>
       <c r="T225" t="inlineStr"/>
